--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20E6A102-9EA7-436B-BABC-5C9EDB054C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F61722-8656-4F74-BFBC-50442BB8CD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
-    <sheet name="v0.9" sheetId="2" r:id="rId2"/>
+    <sheet name="待制作" sheetId="3" r:id="rId2"/>
+    <sheet name="v0.9" sheetId="2" r:id="rId3"/>
+    <sheet name="v0.10" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>工作表名</t>
   </si>
@@ -586,6 +588,38 @@
   </si>
   <si>
     <t>全局状态新增相关字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>详细</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在游戏界面右下角增加波次计数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将敌人生成器的editor界面进行改进，将enemy与enemyminiboss进行合并，在Inspector窗口选择小怪，精英或者Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波数的持续时间显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>挂载miniboss脚本的怪物无法受到攻击，但是却可以攻击玩家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boss攻击音效缺失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>篮球可以攻击boss，飞刀不可以</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -676,7 +710,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -686,6 +720,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -702,10 +742,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1063,6 +1104,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050D8A68-D688-4746-B82B-C6ABAB904C4F}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572029DC-4883-48E6-B541-16C62532E6DB}">
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1376,4 +1451,44 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
+  <dimension ref="A1:C25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="17" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F61722-8656-4F74-BFBC-50442BB8CD68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9172E9AA-1F4F-4175-AF32-2B50BFEFB346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
   <si>
     <t>工作表名</t>
   </si>
@@ -619,7 +619,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>篮球可以攻击boss，飞刀不可以</t>
+    <t>篮球可以攻击boss，飞刀不可以，炸弹不可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每波生成的敌人数量太少，间隔时间太长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimpleSword对Boss不生效</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1134,6 +1142,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1455,7 +1464,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="17" width="30.625" customWidth="1"/>
@@ -1472,23 +1481,49 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C18" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C19" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C20" s="3" t="s">
         <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C21" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C23" s="3" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9172E9AA-1F4F-4175-AF32-2B50BFEFB346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D1A5AD-C0E6-4CE4-A2F7-A6D39227B0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
   <si>
     <t>工作表名</t>
   </si>
@@ -628,6 +628,54 @@
   </si>
   <si>
     <t>SimpleSword对Boss不生效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家攻击小怪时会出现伤害0的异常情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞刀无法正常选定Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>螃蟹boss出现异常，没有技能，无法移动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第16波的boss贴图丢失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第19波的Boss生成的子弹不能正常攻击玩家，子弹不会移动，子弹变成了实体会阻挡玩家，并且导致游戏卡顿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成波数的敌人种类需要进行修改，尤其是第19波变成全部生成boss了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前场景上的怪已经被全部消失时，不用继续等待时间，直接进行下一波生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人被击杀后会多跳多余的一段伤害显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景上的怪已经被全部消失时，直接进行下一波生成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景上的怪已经被全部消失时，直接进行下一波生成，目前发现的情况是在一波怪潮期间，如果是小怪混boss，会出现小怪杀完了，还在等boss生成，导致看上去功能失效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要优化波次生成逻辑，波次列表，怪物生成持续时间，怪物生成刷新间隔，全部刷新完后进行下一波的最大时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏界面的左下角图标，鼠标悬停或者手长按会在上方有技能介绍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -750,11 +798,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1113,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050D8A68-D688-4746-B82B-C6ABAB904C4F}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1125,18 +1174,23 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1518,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="17" width="30.625" customWidth="1"/>
@@ -1521,6 +1575,61 @@
         <v>97</v>
       </c>
     </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C26" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C27" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D1A5AD-C0E6-4CE4-A2F7-A6D39227B0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1BF070-CD65-49C7-A109-CB8CFD010CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
   <si>
     <t>工作表名</t>
   </si>
@@ -676,6 +676,10 @@
   </si>
   <si>
     <t>游戏界面的左下角图标，鼠标悬停或者手长按会在上方有技能介绍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第19波的boss的子弹无法正常攻击玩家</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1518,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="17" width="30.625" customWidth="1"/>
@@ -1630,6 +1634,11 @@
         <v>108</v>
       </c>
     </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1BF070-CD65-49C7-A109-CB8CFD010CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191FC41E-DA85-4760-B319-B18CF07CAAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
   <si>
     <t>工作表名</t>
   </si>
@@ -681,6 +681,45 @@
   <si>
     <t>第19波的boss的子弹无法正常攻击玩家</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重构敌人波次生成逻辑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在是如果有小怪+boss的混合波，会经常出现了场景的怪都打完了，干等boss刷新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>要进行逻辑重构，比如取消小怪+boss的混合波，又或者就把小怪生成完后直接继续生成boss，取消等待的间隔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第19波boss的攻击有异常，攻击到玩家的反馈不正常，受击音效不对，并且玩家被攻击到0血不会结束游戏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炸弹与经验收集道具在地图上掉落时，应该要给玩家视觉引导，告诉玩家道具的大致方向</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v0.10.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 掉落道具视觉引导系统</t>
+  </si>
+  <si>
+    <t>2. 掉落引导开关与设置 UI</t>
+  </si>
+  <si>
+    <t>3. 波次系统/敌人相关变更（摘要）</t>
+  </si>
+  <si>
+    <t>4. Boss 攻击、玩家受击与回血阻断（摘要）</t>
+  </si>
+  <si>
+    <t>5. 文档新增</t>
   </si>
 </sst>
 </file>
@@ -802,12 +841,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1193,7 +1231,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1522,7 +1560,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="17" width="30.625" customWidth="1"/>
@@ -1639,6 +1677,51 @@
         <v>110</v>
       </c>
     </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" t="s">
+        <v>117</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" t="s">
+        <v>119</v>
+      </c>
+      <c r="F52" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191FC41E-DA85-4760-B319-B18CF07CAAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F5C547-C668-4A21-8CD9-CCC3A7890C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
     <sheet name="待制作" sheetId="3" r:id="rId2"/>
-    <sheet name="v0.9" sheetId="2" r:id="rId3"/>
-    <sheet name="v0.10" sheetId="4" r:id="rId4"/>
+    <sheet name="多语言架构（i18n）" sheetId="5" r:id="rId3"/>
+    <sheet name="v0.9" sheetId="2" r:id="rId4"/>
+    <sheet name="v0.10" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1243,6 +1244,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950BEC39-71FA-4C48-BD8E-4C084E37A59B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572029DC-4883-48E6-B541-16C62532E6DB}">
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1558,7 +1569,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
   <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84F5C547-C668-4A21-8CD9-CCC3A7890C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFFBED2-9859-42AA-AC23-6BECAD5B84E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="132">
   <si>
     <t>工作表名</t>
   </si>
@@ -721,6 +721,46 @@
   </si>
   <si>
     <t>5. 文档新增</t>
+  </si>
+  <si>
+    <t>现在启动游戏默认是中文，但是第一次点击切换语言的按钮，会出现文字变成了"ui.settings.xxx"，又或者是根本没有成功多语言切换.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面的返回按键，切换语言的按钮文字，窗口化/全屏文字，标题title,音乐/音效，没有做语言绑定，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uigamestartpanel的“开始游戏”，“设置”，“成就”，“金币升级”没有做语言切换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uigamestartpanel内的成就列表的成就，没有做语言切换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面的放回主菜单文本改成“主菜单”，避免超出按钮显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在中文或者english下第一次加载Game场景，会出现"game.ui.level","game.ui.wave","game.ui.icon",在此场景下点击设置界面的切换语言按钮可以恢复正常显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置界面的“ScreenText”没有做语言转化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game场景初始加载没有问题，但是点击一次切换语言后就出现ui显示错误，出现game.ui.xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uigameoverpanel界面完全没有做多语言切换，uigamepassPAnel同</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoinUpgradePanel下的"BtnClose"按钮的文本没有做多语言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1571,7 +1611,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="17" width="30.625" customWidth="1"/>
@@ -1733,6 +1773,56 @@
         <v>121</v>
       </c>
     </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C60" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C62" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C70" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C71" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C72" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.2">
+      <c r="C74" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCFFBED2-9859-42AA-AC23-6BECAD5B84E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B8F57E-9064-4F88-8ADA-62ACCDE90905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="0" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,8 @@
     <sheet name="多语言架构（i18n）" sheetId="5" r:id="rId3"/>
     <sheet name="v0.9" sheetId="2" r:id="rId4"/>
     <sheet name="v0.10" sheetId="4" r:id="rId5"/>
+    <sheet name="大规模敌人性能优化" sheetId="6" r:id="rId6"/>
+    <sheet name="v0.11" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="154">
   <si>
     <t>工作表名</t>
   </si>
@@ -762,12 +764,131 @@
     <t>CoinUpgradePanel下的"BtnClose"按钮的文本没有做多语言</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>阶段一</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速配置优化（不改架构，立即可量化）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>预计提升：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC 从 1000 → 2000~3000 怪物稳定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC 2000 怪 ≥ 55fps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profiler 对比 GC Alloc/Frame，Memory Profiler 检查内存碎片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GC Alloc &lt; 1KB/frame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段三</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>渐增测试 1k/3k/5k/8k 敌人帧率曲线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC 5000 怪 ≥ 50fps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶段四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全平台基准测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC 10000+ ≥ 60fps, Mobile/Web 5000+ ≥ 30fps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>修改配置后在</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> TestMaxEnemyCount </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>场景运行，对比修改前后帧率</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Game场景的几乎所有UI引用的Key全部失效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人死亡的样式有问题，出现了正方形白色溶解的奇怪形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在玩家死亡后，重新加载游戏，会先出现残留在地图上的敌人，有点吓人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏游玩时，随着游玩时间，Memory会一直上涨，没有上线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GC Heap同理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在GameOver界面会一直加GC和内存，回到GameStart界面会减少一批内存和GC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -849,6 +970,21 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -882,11 +1018,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1828,4 +1965,126 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B667551D-8D89-44CB-9282-6643E8683602}">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="20" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F04812-73C5-4297-8FDC-5E6A3AFBE14E}">
+  <dimension ref="D1:D8"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B8F57E-9064-4F88-8ADA-62ACCDE90905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD47C80E-42A8-49C7-8D9D-29699ED7115D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
     <sheet name="待制作" sheetId="3" r:id="rId2"/>
-    <sheet name="多语言架构（i18n）" sheetId="5" r:id="rId3"/>
-    <sheet name="v0.9" sheetId="2" r:id="rId4"/>
-    <sheet name="v0.10" sheetId="4" r:id="rId5"/>
-    <sheet name="大规模敌人性能优化" sheetId="6" r:id="rId6"/>
-    <sheet name="v0.11" sheetId="7" r:id="rId7"/>
+    <sheet name="操作相关" sheetId="8" r:id="rId3"/>
+    <sheet name="多语言架构（i18n）" sheetId="5" r:id="rId4"/>
+    <sheet name="v0.9" sheetId="2" r:id="rId5"/>
+    <sheet name="v0.10" sheetId="4" r:id="rId6"/>
+    <sheet name="大规模敌人性能优化" sheetId="6" r:id="rId7"/>
+    <sheet name="v0.11" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="162">
   <si>
     <t>工作表名</t>
   </si>
@@ -882,6 +883,36 @@
   <si>
     <t>在GameOver界面会一直加GC和内存，回到GameStart界面会减少一批内存和GC</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Windows</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WEB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安卓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以自动识别屏幕分辨率，并提供不同的分辨率调节档</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安卓端的屏幕分辨率设置主要修改的是渲染分辨率，其次是修改画面比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左下角左侧的全部区域都可以操作控制角色移动</t>
+  </si>
+  <si>
+    <t>默认摇杆是隐藏的，在使用时显示，不用1.5秒后自动隐藏</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1054,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1421,6 +1452,60 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75CA4489-2807-4049-9575-523CA0725CC3}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="15" width="30.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950BEC39-71FA-4C48-BD8E-4C084E37A59B}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1430,7 +1515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{572029DC-4883-48E6-B541-16C62532E6DB}">
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1746,7 +1831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1044432-9EF4-49AA-B227-E8D65110D533}">
   <dimension ref="A1:G74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1967,7 +2052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B667551D-8D89-44CB-9282-6643E8683602}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1990,7 +2075,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
         <v>146</v>
       </c>
       <c r="D2" t="s">
@@ -2042,7 +2127,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69F04812-73C5-4297-8FDC-5E6A3AFBE14E}">
   <dimension ref="D1:D8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>

--- a/Docs/配置表.xlsx
+++ b/Docs/配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unity\Vampire Survivor-like\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD47C80E-42A8-49C7-8D9D-29699ED7115D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51CA117-8B02-4CB5-A80D-14BAC2319D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表名" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="163">
   <si>
     <t>工作表名</t>
   </si>
@@ -913,6 +913,10 @@
   </si>
   <si>
     <t>默认摇杆是隐藏的，在使用时显示，不用1.5秒后自动隐藏</t>
+  </si>
+  <si>
+    <t>如果有机会，做一个ai自动玩游戏的功能，目前打算是纯ai操作行走，在触发升级或其他会暂停游戏的操作时会停下，结束后又回到可以自动操作的状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1413,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050D8A68-D688-4746-B82B-C6ABAB904C4F}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1442,6 +1446,11 @@
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
